--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488175_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488175_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. NAVARRO GARRIDO</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3225</v>
+        <v>1.972</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6836</v>
+        <v>-1.2932</v>
       </c>
       <c r="F2" t="n">
-        <v>0.639</v>
+        <v>3.2651</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0101</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7566</v>
+        <v>0.3192</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7465000000000001</v>
+        <v>0.5572</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5164</v>
+        <v>-0.3804</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0863</v>
+        <v>0.3221</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5699</v>
+        <v>-0.7025</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4937</v>
+        <v>1.2569</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6703</v>
+        <v>-0.0028</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1766</v>
+        <v>1.2597</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1117</v>
+        <v>2.0382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="R2" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.3159</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0386</v>
+        <v>-0.5422</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7362</v>
+        <v>0.858</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.5741</v>
+        <v>-1.2585</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3139</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.8879</v>
+        <v>-1.2585</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2883</v>
+        <v>1.7969</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2883</v>
+        <v>-1.3542</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3.151</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2883</v>
+        <v>0.0068</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2883</v>
+        <v>-0.5722</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2883</v>
+        <v>-0.4723</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2883</v>
+        <v>-0.4214</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.0509</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.479</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.1508</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.6299</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.5863</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.1026</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.6889</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.5744</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2285</v>
+        <v>1.2883</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.9964</v>
+        <v>1.2883</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2249</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0068</v>
+        <v>1.2883</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5722</v>
+        <v>1.2883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4723</v>
+        <v>1.2883</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4214</v>
+        <v>1.2883</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0509</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.479</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1508</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6299</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0179</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7449</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7628</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5744</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. VIOQUE LOMBARDO</t>
+          <t>S. NAVARRO GARRIDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0802</v>
+        <v>1.2837</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.511</v>
+        <v>0.8909</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5912</v>
+        <v>0.3927</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1514</v>
+        <v>1.0101</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4311</v>
+        <v>1.7566</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2796</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.8829</v>
+        <v>0.5164</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2715</v>
+        <v>1.0863</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.5699</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.4937</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1596</v>
+        <v>0.6703</v>
       </c>
       <c r="O5" t="n">
-        <v>0.891</v>
+        <v>-0.1766</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3706</v>
+        <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2142</v>
+        <v>0.7359</v>
       </c>
       <c r="T5" t="n">
-        <v>0.725</v>
+        <v>0.2459</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4892</v>
+        <v>0.4899</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5733</v>
+        <v>-1.5741</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5733</v>
+        <v>0.3139</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.8879</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8904</v>
+        <v>0.5654</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5185</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4089</v>
+        <v>1.5074</v>
       </c>
       <c r="G6" t="n">
         <v>1.6862</v>
@@ -922,13 +922,13 @@
         <v>2.0382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.6211</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3967</v>
+        <v>-0.0267</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5494</v>
+        <v>0.6479</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6302</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>I. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6798</v>
+        <v>0.2776</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3003</v>
+        <v>-1.2398</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9801</v>
+        <v>1.5173</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1779</v>
+        <v>-1.1514</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8645</v>
+        <v>-1.4311</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3133</v>
+        <v>0.2796</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1931</v>
+        <v>-1.8829</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4466</v>
+        <v>-1.2715</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7465000000000001</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9847</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4179</v>
+        <v>-0.1596</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5669</v>
+        <v>0.891</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6676</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9646</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>1.297</v>
+        <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6872</v>
+        <v>0.4116</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1567</v>
+        <v>-0.0037</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5305</v>
+        <v>0.4153</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5177</v>
+        <v>1.5733</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3144</v>
+        <v>1.5733</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.8321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5757</v>
+        <v>0.1524</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2955</v>
+        <v>-0.7785</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8712</v>
+        <v>0.9308</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8764999999999999</v>
+        <v>4.1779</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3192</v>
+        <v>1.8645</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5572</v>
+        <v>2.3133</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3804</v>
+        <v>2.1931</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3221</v>
+        <v>1.4466</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7025</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2569</v>
+        <v>1.9847</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0028</v>
+        <v>0.4179</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2597</v>
+        <v>1.5669</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0382</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3706</v>
+        <v>-2.9646</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4087</v>
+        <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0804</v>
+        <v>0.1598</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5444</v>
+        <v>-0.3214</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4641</v>
+        <v>0.4812</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2585</v>
+        <v>-2.5177</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2585</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3013</v>
+        <v>-0.7924</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7213</v>
+        <v>-1.5571</v>
       </c>
       <c r="F9" t="n">
-        <v>0.42</v>
+        <v>0.7647</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3957</v>
@@ -1156,13 +1156,13 @@
         <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2203</v>
+        <v>0.2885</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1256</v>
+        <v>0.0386</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0948</v>
+        <v>0.2499</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3147</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.061</v>
+        <v>-2.0363</v>
       </c>
       <c r="E10" t="n">
         <v>-1.8314</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2296</v>
+        <v>-0.2049</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7068</v>
@@ -1234,13 +1234,13 @@
         <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2736</v>
       </c>
       <c r="U10" t="n">
-        <v>0.29</v>
+        <v>0.3146</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6294</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8235</v>
+        <v>-6.5336</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.4299</v>
+        <v>-7.7214</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6064</v>
+        <v>1.1878</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9503</v>
@@ -1312,13 +1312,13 @@
         <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4235</v>
+        <v>0.7135</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1279</v>
+        <v>-0.4194</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5514</v>
+        <v>1.1328</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2585</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1204</v>
+        <v>-2.026</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.6324</v>
+        <v>-14.5384</v>
       </c>
       <c r="F12" t="n">
-        <v>12.5121</v>
+        <v>12.5119</v>
       </c>
       <c r="G12" t="n">
-        <v>2.841600000000001</v>
+        <v>2.8416</v>
       </c>
       <c r="H12" t="n">
-        <v>3.264199999999999</v>
+        <v>3.2642</v>
       </c>
       <c r="I12" t="n">
         <v>-0.4229000000000003</v>
@@ -1378,7 +1378,7 @@
         <v>0.2181</v>
       </c>
       <c r="O12" t="n">
-        <v>6.298699999999999</v>
+        <v>6.2987</v>
       </c>
       <c r="P12" t="n">
         <v>-3.7058</v>
@@ -1390,13 +1390,13 @@
         <v>12.0437</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7793</v>
+        <v>3.8736</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4994</v>
+        <v>-1.4051</v>
       </c>
       <c r="U12" t="n">
-        <v>5.278799999999999</v>
+        <v>5.278499999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-5.0354</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.8966</v>
+        <v>11.6338</v>
       </c>
       <c r="E13" t="n">
-        <v>9.251099999999999</v>
+        <v>9.1532</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6455</v>
+        <v>2.4806</v>
       </c>
       <c r="G13" t="n">
         <v>1.3063</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.5885</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1679</v>
+        <v>-0.2658</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0192</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>8.8125</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8668</v>
+        <v>2.6108</v>
       </c>
       <c r="E14" t="n">
         <v>-0.7282999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5951</v>
+        <v>3.3392</v>
       </c>
       <c r="G14" t="n">
         <v>0.4174</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>0.282</v>
+        <v>0.0261</v>
       </c>
       <c r="T14" t="n">
         <v>-0.7486</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0306</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.3144</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3793</v>
+        <v>2.519</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0606</v>
+        <v>-0.3544</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4399</v>
+        <v>2.8734</v>
       </c>
       <c r="G15" t="n">
         <v>1.8516</v>
@@ -1624,13 +1624,13 @@
         <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3987</v>
+        <v>-0.259</v>
       </c>
       <c r="T15" t="n">
+        <v>-0.2764</v>
+      </c>
+      <c r="U15" t="n">
         <v>0.0174</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.4161</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1258</v>
+        <v>2.3784</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1653</v>
+        <v>1.3612</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9605</v>
+        <v>1.0172</v>
       </c>
       <c r="G16" t="n">
         <v>1.5492</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2768</v>
+        <v>-0.0242</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7113</v>
+        <v>-0.5154</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4345</v>
+        <v>0.4912</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6289</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.012</v>
+        <v>1.5595</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2203</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2324</v>
+        <v>1.4861</v>
       </c>
       <c r="G17" t="n">
         <v>0.4835</v>
@@ -1780,13 +1780,13 @@
         <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7685</v>
+        <v>-0.221</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.5605</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0858</v>
+        <v>0.3395</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1204</v>
+        <v>-0.1017</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.153</v>
+        <v>-1.1703</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2734</v>
+        <v>1.0686</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2559</v>
+        <v>0.7837</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2559</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.6943</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0429</v>
+        <v>0.0844</v>
       </c>
       <c r="K19" t="n">
         <v>0.0429</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2989</v>
+        <v>0.6993</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2989</v>
+        <v>0.0464</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.6529</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4504</v>
+        <v>-0.1443</v>
       </c>
       <c r="T19" t="n">
-        <v>0.434</v>
+        <v>-0.3283</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0164</v>
+        <v>0.184</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2569</v>
+        <v>-0.2467</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1703</v>
+        <v>-0.5447</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9134</v>
+        <v>0.298</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7837</v>
+        <v>-0.2559</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08939999999999999</v>
+        <v>-0.2559</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6943</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0844</v>
+        <v>0.0429</v>
       </c>
       <c r="K20" t="n">
         <v>0.0429</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6993</v>
+        <v>-0.2989</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0464</v>
+        <v>-0.2989</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6529</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2994</v>
+        <v>0.0833</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3283</v>
+        <v>0.0423</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0288</v>
+        <v>0.041</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1549</v>
+        <v>-1.9124</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9076</v>
+        <v>-4.0049</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2473</v>
+        <v>2.0925</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1894</v>
+        <v>-1.112</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-1.1966</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4147</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J21" t="n">
+        <v>-1.5681</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.9152</v>
+      </c>
+      <c r="L21" t="n">
         <v>-0.6529</v>
       </c>
-      <c r="K21" t="n">
-        <v>-0.6529</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
-        <v>-0.5366</v>
+        <v>0.456</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1219</v>
+        <v>-0.2814</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4147</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-2.0382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4096</v>
+        <v>-0.7443</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3283</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0813</v>
+        <v>-0.0311</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3299</v>
+        <v>-1.9831</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2008</v>
+        <v>-1.8097</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8709</v>
+        <v>-0.1735</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.112</v>
+        <v>-1.1894</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1966</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.4147</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5681</v>
+        <v>-0.6529</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9152</v>
+        <v>-0.6529</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6529</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.456</v>
+        <v>-0.5366</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2814</v>
+        <v>-0.1219</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7374000000000001</v>
+        <v>-0.4147</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3706</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0382</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1617</v>
+        <v>-0.2378</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.909</v>
+        <v>-0.2304</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2527</v>
+        <v>-0.0075</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8552</v>
+        <v>-2.8472</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5767</v>
+        <v>-5.6747</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7215</v>
+        <v>2.8274</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1895</v>
@@ -2248,13 +2248,13 @@
         <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2564</v>
+        <v>-0.2484</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.6277</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2733</v>
+        <v>0.3793</v>
       </c>
       <c r="V23" t="n">
         <v>0.6289</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3752</v>
+        <v>-2.8598</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6122</v>
+        <v>-3.3184</v>
       </c>
       <c r="F24" t="n">
-        <v>0.237</v>
+        <v>0.4586</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4931</v>
@@ -2326,13 +2326,13 @@
         <v>1.4823</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4206</v>
+        <v>0.0948</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8754</v>
+        <v>-0.5816</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4549</v>
+        <v>0.6765</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9439</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9304</v>
+        <v>-6.9465</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9206</v>
+        <v>-6.1164</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0099</v>
+        <v>-0.83</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6153</v>
@@ -2404,13 +2404,13 @@
         <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3713</v>
+        <v>-0.3874</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2773</v>
+        <v>-0.4731</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.094</v>
+        <v>0.0858</v>
       </c>
       <c r="V25" t="n">
         <v>-2.8321</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.120499999999999</v>
+        <v>4.426199999999998</v>
       </c>
       <c r="E26" t="n">
         <v>-12.5119</v>
       </c>
       <c r="F26" t="n">
-        <v>15.6324</v>
+        <v>16.9381</v>
       </c>
       <c r="G26" t="n">
         <v>-2.841400000000001</v>
@@ -2458,7 +2458,7 @@
         <v>-6.5168</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2181999999999999</v>
+        <v>-0.2181999999999995</v>
       </c>
       <c r="L26" t="n">
         <v>-6.298699999999999</v>
@@ -2482,13 +2482,13 @@
         <v>15.7496</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.7793</v>
+        <v>-1.4737</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.278700000000001</v>
+        <v>-5.2787</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4994</v>
+        <v>3.8051</v>
       </c>
       <c r="V26" t="n">
         <v>5.035299999999999</v>
